--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,18 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,12 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10736</v>
+        <v>16997</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11095</v>
+        <v>18526</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-359</v>
+        <v>-1529</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8570</v>
+        <v>14881</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14090</v>
+        <v>16532</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5520</v>
+        <v>-1651</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +599,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -645,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9398</v>
+        <v>14881</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14090</v>
+        <v>16532</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4692</v>
+        <v>-1651</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +644,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -690,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>17457</v>
+        <v>14881</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18561</v>
+        <v>15044</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1104</v>
+        <v>-163</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -713,546 +695,6 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>17457</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20562</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-3105</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19-AUG-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>14366</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-2208</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20-AUG-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>14366</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-2208</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26-AUG-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>10736</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>15083</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-4347</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27-AUG-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>9398</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>15083</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-5685</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>02-SEP-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>8570</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-8004</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>03-SEP-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9398</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-7176</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>8570</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-8004</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>7603</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-8971</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>7355</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-9219</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>7355</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>16574</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-9219</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>7355</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>9108</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-1753</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6810BC78-50CF-46FD-8D8F-719B91DBA610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AAF03E-D70A-44B2-BD87-0952731E1916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -69,16 +69,13 @@
     <t>Nile Air NP-119</t>
   </si>
   <si>
-    <t>MED</t>
+    <t>LOW</t>
   </si>
   <si>
     <t>EGP</t>
   </si>
   <si>
     <t>05-AUG-26</t>
-  </si>
-  <si>
-    <t>LOW</t>
   </si>
   <si>
     <t>06-AUG-26</t>
@@ -183,7 +180,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,12 +191,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF3498DB"/>
         <bgColor rgb="FF3498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -242,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -254,9 +245,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -623,13 +611,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>14881</v>
+        <v>16996</v>
       </c>
       <c r="E2" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F2" s="2">
-        <v>-3645</v>
+        <v>-1529</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -658,13 +646,13 @@
         <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>14881</v>
+        <v>14880</v>
       </c>
       <c r="E3" s="2">
         <v>15044</v>
       </c>
       <c r="F3" s="2">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -675,8 +663,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -684,22 +672,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D4" s="2">
-        <v>14881</v>
+        <v>14880</v>
       </c>
       <c r="E4" s="2">
         <v>15044</v>
       </c>
       <c r="F4" s="2">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="G4" s="2">
         <v>30</v>
@@ -710,8 +698,8 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -719,7 +707,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -728,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="D5" s="2">
-        <v>14881</v>
+        <v>14880</v>
       </c>
       <c r="E5" s="2">
-        <v>15044</v>
+        <v>16532</v>
       </c>
       <c r="F5" s="2">
-        <v>-163</v>
+        <v>-1652</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -745,8 +733,8 @@
       <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>17</v>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -754,7 +742,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -780,8 +768,8 @@
       <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -789,13 +777,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>5501</v>
@@ -815,8 +803,8 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -824,7 +812,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -850,8 +838,8 @@
       <c r="I8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>17</v>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -859,7 +847,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -885,8 +873,8 @@
       <c r="I9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>17</v>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -894,13 +882,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2">
         <v>5501</v>
@@ -920,8 +908,8 @@
       <c r="I10" s="2">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>17</v>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -929,7 +917,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -955,8 +943,8 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>17</v>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -964,13 +952,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2">
         <v>5501</v>
@@ -990,8 +978,8 @@
       <c r="I12" s="2">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>17</v>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -999,7 +987,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1025,8 +1013,8 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+      <c r="J13" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1034,13 +1022,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2">
         <v>5501</v>
@@ -1060,8 +1048,8 @@
       <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>17</v>
+      <c r="J14" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1069,7 +1057,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1095,8 +1083,8 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>17</v>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1104,13 +1092,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
         <v>5501</v>
@@ -1130,8 +1118,8 @@
       <c r="I16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>17</v>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1139,7 +1127,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1165,8 +1153,8 @@
       <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>17</v>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1174,13 +1162,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2">
         <v>5501</v>
@@ -1200,8 +1188,8 @@
       <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>34</v>
+      <c r="J18" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1209,7 +1197,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1235,8 +1223,8 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>34</v>
+      <c r="J19" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1244,13 +1232,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2">
         <v>5501</v>
@@ -1270,8 +1258,8 @@
       <c r="I20" s="2">
         <v>0</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>34</v>
+      <c r="J20" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1279,7 +1267,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1305,8 +1293,8 @@
       <c r="I21" s="2">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>17</v>
+      <c r="J21" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1314,13 +1302,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
         <v>5501</v>
@@ -1340,8 +1328,8 @@
       <c r="I22" s="2">
         <v>0</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>17</v>
+      <c r="J22" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1349,7 +1337,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1375,8 +1363,8 @@
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>17</v>
+      <c r="J23" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1384,13 +1372,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="2">
         <v>5501</v>
@@ -1410,8 +1398,8 @@
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>17</v>
+      <c r="J24" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1419,7 +1407,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1445,8 +1433,8 @@
       <c r="I25" s="2">
         <v>0</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>17</v>
+      <c r="J25" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1454,13 +1442,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="2">
         <v>5501</v>
@@ -1480,8 +1468,8 @@
       <c r="I26" s="2">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>17</v>
+      <c r="J26" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1489,7 +1477,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1515,8 +1503,8 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>17</v>
+      <c r="J27" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
